--- a/tame_output/ON/bt/strategyON_20231019.xlsx
+++ b/tame_output/ON/bt/strategyON_20231019.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.5%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1754"/>
+  <dimension ref="A1:G1755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41852,7 +41852,7 @@
         <v>45216</v>
       </c>
       <c r="B1754" t="n">
-        <v>2.863148958350867</v>
+        <v>2.864454936419492</v>
       </c>
       <c r="C1754" t="n">
         <v>2.957874679524909</v>
@@ -41868,6 +41868,29 @@
       </c>
       <c r="G1754" t="n">
         <v>4.255118746393969</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="2" t="n">
+        <v>45217</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>2.85500603633627</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>2.95420083304114</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>1.575426665115271</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>3.584015074773502</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>2.164300990818542</v>
+      </c>
+      <c r="G1755" t="n">
+        <v>4.252781427532267</v>
       </c>
     </row>
   </sheetData>
